--- a/Result/profitability/8279.xlsx
+++ b/Result/profitability/8279.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM52"/>
+  <dimension ref="A1:AM53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7038,6 +7038,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>8279</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>593</v>
+      </c>
+      <c r="D53" t="n">
+        <v>407</v>
+      </c>
+      <c r="E53" t="n">
+        <v>187</v>
+      </c>
+      <c r="F53" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="G53" t="n">
+        <v>84</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>14.17%</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" t="n">
+        <v>86</v>
+      </c>
+      <c r="K53" t="n">
+        <v>70</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.3325</v>
+      </c>
+      <c r="N53" t="n">
+        <v>34.0075</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1.089430894308943</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>-1.509999999999998</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-0.04579921140430687</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>-0.6600000000000001</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>-0.2043343653250774</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>-4.799999999999997</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>-0.132377275234418</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK53" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
